--- a/graficos/LDA_mejores_umass.xlsx
+++ b/graficos/LDA_mejores_umass.xlsx
@@ -61,18 +61,18 @@
     <t>orps_lim_dictamen_K9_-</t>
   </si>
   <si>
+    <t>comisión</t>
+  </si>
+  <si>
+    <t>comisión_dictamen_K5_-</t>
+  </si>
+  <si>
     <t>orps</t>
   </si>
   <si>
     <t>orps_dictamen_K5_-</t>
   </si>
   <si>
-    <t>comisión</t>
-  </si>
-  <si>
-    <t>comisión_dictamen_K5_-</t>
-  </si>
-  <si>
     <t>orps_lim_dictamen_K10_-</t>
   </si>
   <si>
@@ -103,28 +103,28 @@
     <t>todos_dictamen_K12_-</t>
   </si>
   <si>
+    <t>comisión_dictamen_K6_-</t>
+  </si>
+  <si>
     <t>orps_dictamen_K6_-</t>
   </si>
   <si>
-    <t>comisión_dictamen_K6_-</t>
+    <t>comisión_contenido_K3_-</t>
   </si>
   <si>
     <t>orps_contenido_K3_-</t>
   </si>
   <si>
-    <t>comisión_contenido_K3_-</t>
-  </si>
-  <si>
     <t>orps_lim_dictamen_K13_-</t>
   </si>
   <si>
     <t>todos_dictamen_K11_-</t>
   </si>
   <si>
-    <t>denuncia_dictamen</t>
-  </si>
-  <si>
-    <t>todos_denuncia_dictamen_K4_-</t>
+    <t>antecedentes_dictamen</t>
+  </si>
+  <si>
+    <t>todos_antecedentes_dictamen_K4_-</t>
   </si>
   <si>
     <t>todos_dictamen_K16_-</t>
